--- a/库存物料清单.xlsx
+++ b/库存物料清单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PCB_pro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PCB_pro\Material_物料清单\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E806FD-B23E-4929-B444-B69BE415E942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CF42B4-E02B-418D-95FF-74C2C15E672B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="元件盘" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="141">
   <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,10 +474,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SOD323 SJ(5817)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SOD123 S4(SD103AWS)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -487,14 +483,6 @@
   </si>
   <si>
     <t>WCH340E USB串口芯片</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOT23-6 V05(SRV05)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOT23 EL61(E8DA6V1L)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -646,15 +634,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>FPC14P/18P/40P/6P/50P座</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>USB外壳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10K插线电阻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOT23-6 丝印V05(SRV05)
+TVS二极管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOT23 丝印EL61(E8DA6V1L/ESDA6V1L)
+ESD/TVS静电保护管 贴片三极管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOD323 丝印SJ(5817)
+肖特基二极管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0603电阻
+10Ω  1%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -960,48 +968,60 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1028,18 +1048,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1334,16 +1342,16 @@
     <col min="1" max="1" width="8.6640625" style="1"/>
     <col min="2" max="2" width="4.4140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="1" customWidth="1"/>
     <col min="5" max="6" width="22.9140625" style="1" customWidth="1"/>
     <col min="7" max="8" width="27" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="36.9140625" style="1" customWidth="1"/>
     <col min="10" max="10" width="20.6640625" style="1" customWidth="1"/>
     <col min="11" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" s="41">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
@@ -1374,7 +1382,7 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A3" s="41"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="8">
         <v>1</v>
       </c>
@@ -1404,7 +1412,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A4" s="41"/>
+      <c r="A4" s="18"/>
       <c r="B4" s="8">
         <v>2</v>
       </c>
@@ -1434,7 +1442,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A5" s="41"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="8">
         <v>3</v>
       </c>
@@ -1464,7 +1472,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" s="42">
+      <c r="A8" s="19">
         <v>2</v>
       </c>
       <c r="B8" s="9"/>
@@ -1494,7 +1502,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="42"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="12">
         <v>1</v>
       </c>
@@ -1513,14 +1521,16 @@
       <c r="G9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="6" t="s">
+        <v>140</v>
+      </c>
       <c r="I9" s="5"/>
       <c r="J9" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A10" s="42"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="12">
         <v>2</v>
       </c>
@@ -1548,7 +1558,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A11" s="42"/>
+      <c r="A11" s="19"/>
       <c r="B11" s="12">
         <v>3</v>
       </c>
@@ -1576,7 +1586,7 @@
       <c r="J11" s="5"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A14" s="43">
+      <c r="A14" s="20">
         <v>3</v>
       </c>
       <c r="B14" s="13"/>
@@ -1606,7 +1616,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A15" s="43"/>
+      <c r="A15" s="20"/>
       <c r="B15" s="13">
         <v>1</v>
       </c>
@@ -1622,7 +1632,7 @@
         <v>54</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>55</v>
@@ -1632,7 +1642,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A16" s="43"/>
+      <c r="A16" s="20"/>
       <c r="B16" s="13">
         <v>2</v>
       </c>
@@ -1662,7 +1672,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A17" s="43"/>
+      <c r="A17" s="20"/>
       <c r="B17" s="13">
         <v>3</v>
       </c>
@@ -1690,7 +1700,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" s="42">
+      <c r="A20" s="19">
         <v>4</v>
       </c>
       <c r="B20" s="9"/>
@@ -1720,7 +1730,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A21" s="42"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="12">
         <v>1</v>
       </c>
@@ -1750,7 +1760,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A22" s="42"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="12">
         <v>2</v>
       </c>
@@ -1778,7 +1788,7 @@
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A23" s="42"/>
+      <c r="A23" s="19"/>
       <c r="B23" s="12">
         <v>3</v>
       </c>
@@ -1808,7 +1818,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A26" s="44">
+      <c r="A26" s="21">
         <v>5</v>
       </c>
       <c r="B26" s="14"/>
@@ -1838,7 +1848,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A27" s="44"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="16">
         <v>1</v>
       </c>
@@ -1846,52 +1856,52 @@
         <v>95</v>
       </c>
       <c r="D27" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="F27" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>102</v>
-      </c>
     </row>
     <row r="28" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A28" s="44"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="16">
         <v>2</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A29" s="44"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="16">
         <v>3</v>
       </c>
@@ -1902,10 +1912,10 @@
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1941,520 +1951,500 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="18">
+      <c r="A2" s="35">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="E2" s="24"/>
-      <c r="F2" s="19" t="s">
+      <c r="B2" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="27"/>
+      <c r="F2" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="G2" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="K2" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="L2" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="M2" s="22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A3" s="35"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A4" s="35"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A5" s="35"/>
+      <c r="B5" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="K2" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="L2" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="M2" s="19" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="18"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A4" s="18"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="18"/>
-      <c r="B5" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
     </row>
     <row r="6" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="18"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
       <c r="H6" s="17">
         <v>1</v>
       </c>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" s="18"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A8" s="18"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A9" s="18"/>
-      <c r="B9" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="24"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="27"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A10" s="18"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="27"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="30"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A11" s="18"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="30"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="33"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" s="18">
+      <c r="A15" s="35">
         <v>2</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="G15" s="19"/>
-      <c r="I15" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="J15" s="19" t="s">
+      <c r="B15" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="27"/>
+      <c r="D15" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" s="27"/>
+      <c r="F15" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="G15" s="22"/>
+      <c r="I15" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="L15" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="K15" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="L15" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="M15" s="19" t="s">
-        <v>111</v>
+      <c r="M15" s="22" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" s="18"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A17" s="18"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A18" s="18"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
     </row>
     <row r="19" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A19" s="18"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
       <c r="H19" s="17">
         <v>2</v>
       </c>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="23"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A20" s="18"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="23"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A21" s="18"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="23"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A22" s="18"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="34"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="38"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A23" s="18"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="37"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="41"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A24" s="18"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="44"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="24"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A27" s="18">
+      <c r="A27" s="35">
         <v>3</v>
       </c>
-      <c r="B27" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="E27" s="24"/>
-      <c r="F27" s="19" t="s">
+      <c r="B27" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="27"/>
+      <c r="D27" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="27"/>
+      <c r="F27" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="I27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="M27" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="G27" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="I27" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="K27" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="L27" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="M27" s="19" t="s">
-        <v>132</v>
-      </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A28" s="18"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A29" s="18"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="23"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A30" s="18"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+      <c r="M30" s="23"/>
     </row>
     <row r="31" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A31" s="18"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
       <c r="H31" s="17">
         <v>3</v>
       </c>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A32" s="18"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
+      <c r="A32" s="35"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="23"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
+      <c r="M32" s="23"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A33" s="18"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
+      <c r="M33" s="23"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A34" s="18"/>
-      <c r="B34" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="24"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="27"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
+      <c r="K34" s="23"/>
+      <c r="L34" s="23"/>
+      <c r="M34" s="23"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A35" s="18"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="27"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
+      <c r="A35" s="35"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="30"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="23"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A36" s="18"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="30"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="21"/>
+      <c r="A36" s="35"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="33"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="K27:K36"/>
-    <mergeCell ref="L27:L36"/>
-    <mergeCell ref="M27:M36"/>
-    <mergeCell ref="I27:I36"/>
-    <mergeCell ref="B34:G36"/>
-    <mergeCell ref="D27:E29"/>
-    <mergeCell ref="F27:F33"/>
-    <mergeCell ref="G27:G33"/>
-    <mergeCell ref="B30:E33"/>
-    <mergeCell ref="J27:J36"/>
-    <mergeCell ref="I2:I11"/>
-    <mergeCell ref="J2:J11"/>
-    <mergeCell ref="K2:K11"/>
-    <mergeCell ref="L2:L11"/>
-    <mergeCell ref="M2:M11"/>
-    <mergeCell ref="I15:I24"/>
-    <mergeCell ref="J15:J24"/>
-    <mergeCell ref="K15:K24"/>
-    <mergeCell ref="L15:L24"/>
-    <mergeCell ref="M15:M24"/>
     <mergeCell ref="A15:A24"/>
     <mergeCell ref="A27:A36"/>
     <mergeCell ref="A2:A11"/>
@@ -2471,6 +2461,26 @@
     <mergeCell ref="B18:E21"/>
     <mergeCell ref="B22:G24"/>
     <mergeCell ref="B27:C29"/>
+    <mergeCell ref="I15:I24"/>
+    <mergeCell ref="J15:J24"/>
+    <mergeCell ref="K15:K24"/>
+    <mergeCell ref="L15:L24"/>
+    <mergeCell ref="M15:M24"/>
+    <mergeCell ref="I2:I11"/>
+    <mergeCell ref="J2:J11"/>
+    <mergeCell ref="K2:K11"/>
+    <mergeCell ref="L2:L11"/>
+    <mergeCell ref="M2:M11"/>
+    <mergeCell ref="K27:K36"/>
+    <mergeCell ref="L27:L36"/>
+    <mergeCell ref="M27:M36"/>
+    <mergeCell ref="I27:I36"/>
+    <mergeCell ref="B34:G36"/>
+    <mergeCell ref="D27:E29"/>
+    <mergeCell ref="F27:F33"/>
+    <mergeCell ref="G27:G33"/>
+    <mergeCell ref="B30:E33"/>
+    <mergeCell ref="J27:J36"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/库存物料清单.xlsx
+++ b/库存物料清单.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PCB_pro\Material_物料清单\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PCB_pro\Material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CF42B4-E02B-418D-95FF-74C2C15E672B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2827C101-B4BB-4A0A-8E23-5E8B0B623F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="142">
   <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -663,6 +663,11 @@
   <si>
     <t>0603电阻
 10Ω  1%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1206磁珠
+0Ω</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -980,6 +985,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1016,38 +1024,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1583,7 +1588,9 @@
       <c r="I11" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="J11" s="5"/>
+      <c r="J11" s="6" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" s="20">
@@ -1951,500 +1958,520 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="35">
+      <c r="A2" s="22">
         <v>1</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="25" t="s">
+      <c r="C2" s="28"/>
+      <c r="D2" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="22" t="s">
+      <c r="E2" s="28"/>
+      <c r="F2" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="L2" s="34" t="s">
+      <c r="L2" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="M2" s="22" t="s">
+      <c r="M2" s="23" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="35"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A4" s="35"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="35"/>
-      <c r="B5" s="25" t="s">
+      <c r="A5" s="22"/>
+      <c r="B5" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
     </row>
     <row r="6" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="35"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
       <c r="H6" s="17">
         <v>1</v>
       </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" s="35"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A8" s="35"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A9" s="35"/>
-      <c r="B9" s="25" t="s">
+      <c r="A9" s="22"/>
+      <c r="B9" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="27"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="28"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A10" s="35"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="30"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="31"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A11" s="35"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="33"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="34"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" s="35">
+      <c r="A15" s="22">
         <v>2</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="25" t="s">
+      <c r="C15" s="28"/>
+      <c r="D15" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="22" t="s">
+      <c r="E15" s="28"/>
+      <c r="F15" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="I15" s="22" t="s">
+      <c r="G15" s="23"/>
+      <c r="I15" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="J15" s="22" t="s">
+      <c r="J15" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="K15" s="22" t="s">
+      <c r="K15" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="L15" s="22" t="s">
+      <c r="L15" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="M15" s="22" t="s">
+      <c r="M15" s="23" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" s="35"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A17" s="35"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A18" s="35"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
     </row>
     <row r="19" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A19" s="35"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="17">
         <v>2</v>
       </c>
-      <c r="I19" s="23"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A20" s="35"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A21" s="35"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A22" s="35"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="37"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A23" s="35"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="40"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A24" s="35"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="44"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A27" s="35">
+      <c r="A27" s="22">
         <v>3</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="25" t="s">
+      <c r="C27" s="28"/>
+      <c r="D27" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="E27" s="27"/>
-      <c r="F27" s="22" t="s">
+      <c r="E27" s="28"/>
+      <c r="F27" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="G27" s="22" t="s">
+      <c r="G27" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="I27" s="22" t="s">
+      <c r="I27" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="J27" s="22" t="s">
+      <c r="J27" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="K27" s="22" t="s">
+      <c r="K27" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="L27" s="22" t="s">
+      <c r="L27" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="M27" s="22" t="s">
+      <c r="M27" s="23" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A28" s="35"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="24"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A29" s="35"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="24"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A30" s="35"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+      <c r="M30" s="24"/>
     </row>
     <row r="31" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A31" s="35"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
       <c r="H31" s="17">
         <v>3</v>
       </c>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A32" s="35"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="23"/>
-      <c r="M32" s="23"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="24"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A33" s="35"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A34" s="35"/>
-      <c r="B34" s="25" t="s">
+      <c r="A34" s="22"/>
+      <c r="B34" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="27"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="28"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="24"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A35" s="35"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="30"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="31"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A36" s="35"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="33"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
+      <c r="A36" s="22"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="34"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="K27:K36"/>
+    <mergeCell ref="L27:L36"/>
+    <mergeCell ref="M27:M36"/>
+    <mergeCell ref="I27:I36"/>
+    <mergeCell ref="B34:G36"/>
+    <mergeCell ref="D27:E29"/>
+    <mergeCell ref="F27:F33"/>
+    <mergeCell ref="G27:G33"/>
+    <mergeCell ref="B30:E33"/>
+    <mergeCell ref="J27:J36"/>
+    <mergeCell ref="I2:I11"/>
+    <mergeCell ref="J2:J11"/>
+    <mergeCell ref="K2:K11"/>
+    <mergeCell ref="L2:L11"/>
+    <mergeCell ref="M2:M11"/>
+    <mergeCell ref="I15:I24"/>
+    <mergeCell ref="J15:J24"/>
+    <mergeCell ref="K15:K24"/>
+    <mergeCell ref="L15:L24"/>
+    <mergeCell ref="M15:M24"/>
     <mergeCell ref="A15:A24"/>
     <mergeCell ref="A27:A36"/>
     <mergeCell ref="A2:A11"/>
@@ -2461,26 +2488,6 @@
     <mergeCell ref="B18:E21"/>
     <mergeCell ref="B22:G24"/>
     <mergeCell ref="B27:C29"/>
-    <mergeCell ref="I15:I24"/>
-    <mergeCell ref="J15:J24"/>
-    <mergeCell ref="K15:K24"/>
-    <mergeCell ref="L15:L24"/>
-    <mergeCell ref="M15:M24"/>
-    <mergeCell ref="I2:I11"/>
-    <mergeCell ref="J2:J11"/>
-    <mergeCell ref="K2:K11"/>
-    <mergeCell ref="L2:L11"/>
-    <mergeCell ref="M2:M11"/>
-    <mergeCell ref="K27:K36"/>
-    <mergeCell ref="L27:L36"/>
-    <mergeCell ref="M27:M36"/>
-    <mergeCell ref="I27:I36"/>
-    <mergeCell ref="B34:G36"/>
-    <mergeCell ref="D27:E29"/>
-    <mergeCell ref="F27:F33"/>
-    <mergeCell ref="G27:G33"/>
-    <mergeCell ref="B30:E33"/>
-    <mergeCell ref="J27:J36"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/库存物料清单.xlsx
+++ b/库存物料清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PCB_pro\Material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2827C101-B4BB-4A0A-8E23-5E8B0B623F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D9432A-4EC4-426F-B5CE-4A96AF8C7E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="元件盘" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="144">
   <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,10 +474,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SOD123 S4(SD103AWS)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>WCH340N USB串口芯片</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -515,10 +511,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SW_5.8x5.8 锁定开关</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3位带小数点数码管</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -564,10 +556,6 @@
   </si>
   <si>
     <t>STM32F103VET6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.54mm弯针双排带扣/带鼻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -668,6 +656,29 @@
   <si>
     <t>1206磁珠
 0Ω</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.8x5.8mm6脚锁定开关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOD123 S4(SD103AWS)
+1206封装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S4/1N5819(SOD232)
+0805封装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0603电阻
+22Ω  1%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.54mm 2x10弯针双排带扣/带鼻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -930,7 +941,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -972,6 +983,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1356,7 +1370,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" s="18">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
@@ -1387,7 +1401,7 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A3" s="18"/>
+      <c r="A3" s="19"/>
       <c r="B3" s="8">
         <v>1</v>
       </c>
@@ -1417,7 +1431,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A4" s="18"/>
+      <c r="A4" s="19"/>
       <c r="B4" s="8">
         <v>2</v>
       </c>
@@ -1447,7 +1461,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A5" s="18"/>
+      <c r="A5" s="19"/>
       <c r="B5" s="8">
         <v>3</v>
       </c>
@@ -1477,7 +1491,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" s="19">
+      <c r="A8" s="20">
         <v>2</v>
       </c>
       <c r="B8" s="9"/>
@@ -1507,7 +1521,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="19"/>
+      <c r="A9" s="20"/>
       <c r="B9" s="12">
         <v>1</v>
       </c>
@@ -1527,15 +1541,17 @@
         <v>36</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="I9" s="5"/>
+        <v>137</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="J9" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A10" s="19"/>
+      <c r="A10" s="20"/>
       <c r="B10" s="12">
         <v>2</v>
       </c>
@@ -1563,7 +1579,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A11" s="19"/>
+      <c r="A11" s="20"/>
       <c r="B11" s="12">
         <v>3</v>
       </c>
@@ -1589,11 +1605,11 @@
         <v>51</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A14" s="20">
+      <c r="A14" s="21">
         <v>3</v>
       </c>
       <c r="B14" s="13"/>
@@ -1623,7 +1639,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A15" s="20"/>
+      <c r="A15" s="21"/>
       <c r="B15" s="13">
         <v>1</v>
       </c>
@@ -1639,7 +1655,7 @@
         <v>54</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>55</v>
@@ -1649,7 +1665,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.45">
-      <c r="A16" s="20"/>
+      <c r="A16" s="21"/>
       <c r="B16" s="13">
         <v>2</v>
       </c>
@@ -1679,7 +1695,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A17" s="20"/>
+      <c r="A17" s="21"/>
       <c r="B17" s="13">
         <v>3</v>
       </c>
@@ -1707,7 +1723,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" s="19">
+      <c r="A20" s="20">
         <v>4</v>
       </c>
       <c r="B20" s="9"/>
@@ -1737,7 +1753,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A21" s="19"/>
+      <c r="A21" s="20"/>
       <c r="B21" s="12">
         <v>1</v>
       </c>
@@ -1767,7 +1783,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A22" s="19"/>
+      <c r="A22" s="20"/>
       <c r="B22" s="12">
         <v>2</v>
       </c>
@@ -1795,7 +1811,7 @@
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A23" s="19"/>
+      <c r="A23" s="20"/>
       <c r="B23" s="12">
         <v>3</v>
       </c>
@@ -1825,7 +1841,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A26" s="21">
+      <c r="A26" s="22">
         <v>5</v>
       </c>
       <c r="B26" s="14"/>
@@ -1855,7 +1871,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A27" s="21"/>
+      <c r="A27" s="22"/>
       <c r="B27" s="16">
         <v>1</v>
       </c>
@@ -1863,52 +1879,55 @@
         <v>95</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="F27" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>99</v>
-      </c>
     </row>
     <row r="28" spans="1:10" ht="33" x14ac:dyDescent="0.45">
-      <c r="A28" s="21"/>
+      <c r="A28" s="22"/>
       <c r="B28" s="16">
         <v>2</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="F28" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="G28" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A29" s="21"/>
+      <c r="A29" s="22"/>
       <c r="B29" s="16">
         <v>3</v>
       </c>
@@ -1919,11 +1938,9 @@
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>105</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="J29" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1952,503 +1969,505 @@
     <col min="9" max="9" width="19.9140625" style="1" customWidth="1"/>
     <col min="10" max="10" width="20.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="20.83203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="24" style="1" customWidth="1"/>
+    <col min="12" max="12" width="29.5" style="1" customWidth="1"/>
     <col min="13" max="13" width="19.6640625" style="1" customWidth="1"/>
     <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="22">
+      <c r="A2" s="23">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2" s="28"/>
-      <c r="F2" s="23" t="s">
+      <c r="B2" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="29"/>
+      <c r="F2" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="I2" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="J2" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="K2" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="L2" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="M2" s="23" t="s">
-        <v>120</v>
+      <c r="J2" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="L2" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="22"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A4" s="22"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
+      <c r="A4" s="23"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="22"/>
-      <c r="B5" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
     </row>
     <row r="6" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="22"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
       <c r="H6" s="17">
         <v>1</v>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" s="22"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A8" s="22"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A9" s="22"/>
-      <c r="B9" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="28"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A10" s="22"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="31"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="32"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A11" s="22"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="34"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="35"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" s="22">
+      <c r="A15" s="23">
         <v>2</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="G15" s="23"/>
-      <c r="I15" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="J15" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="K15" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="L15" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="M15" s="23" t="s">
-        <v>108</v>
+      <c r="B15" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="L15" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="M15" s="24" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" s="22"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A17" s="22"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A18" s="22"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
     </row>
     <row r="19" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A19" s="22"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
       <c r="H19" s="17">
         <v>2</v>
       </c>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A20" s="22"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A21" s="22"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A22" s="22"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="37"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="38"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A23" s="22"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="41"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A24" s="22"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="43"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="44"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A27" s="22">
+      <c r="A27" s="23">
         <v>3</v>
       </c>
-      <c r="B27" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="E27" s="28"/>
-      <c r="F27" s="23" t="s">
+      <c r="B27" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="29"/>
+      <c r="D27" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="29"/>
+      <c r="F27" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="I27" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="J27" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="K27" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="L27" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="M27" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="G27" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="I27" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="J27" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="K27" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="L27" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="M27" s="23" t="s">
-        <v>129</v>
-      </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A28" s="22"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
+      <c r="A28" s="23"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A29" s="22"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A30" s="22"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="24"/>
+      <c r="A30" s="23"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
     </row>
     <row r="31" spans="1:13" ht="27.5" x14ac:dyDescent="0.45">
-      <c r="A31" s="22"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
+      <c r="A31" s="23"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
       <c r="H31" s="17">
         <v>3</v>
       </c>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A32" s="22"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A33" s="22"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="24"/>
+      <c r="A33" s="23"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A34" s="22"/>
-      <c r="B34" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="28"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
+      <c r="A34" s="23"/>
+      <c r="B34" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="29"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A35" s="22"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="31"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="32"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A36" s="22"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="34"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="25"/>
-      <c r="L36" s="25"/>
-      <c r="M36" s="25"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="35"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="36">
